--- a/FVS_inputs/FVS_Input_Template.xlsx
+++ b/FVS_inputs/FVS_Input_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\showalt_d\Documents\GitHub\Apiary_LRR\FVS_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72508DE1-8658-4974-8698-F7A23DC42236}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE999350-2A32-473B-9BA0-309A4412A374}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FVS_GroupAddFilesAndKeywords" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="109">
   <si>
     <t>GROUPS</t>
   </si>
@@ -32,21 +32,6 @@
   </si>
   <si>
     <t>FVSKEYWORDS</t>
-  </si>
-  <si>
-    <t>All_Stands</t>
-  </si>
-  <si>
-    <t>Database_x000D_
-DSNin_x000D_
-FVS_Data1(42).db_x000D_
-StandSQL_x000D_
-SELECT * FROM FVS_StandInit WHERE Stand_CN = '%Stand_CN%'_x000D_
-EndSQL_x000D_
-TreeSQL_x000D_
-SELECT * FROM FVS_TreeInit WHERE Stand_CN = '%Stand_CN%'_x000D_
-EndSQL_x000D_
-END</t>
   </si>
   <si>
     <t>STAND_CN</t>
@@ -400,8 +385,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,12 +719,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
+      <c r="C2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -750,16 +733,16 @@
   <sheetData>
     <row r="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -771,187 +754,187 @@
         <v>2</v>
       </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>41</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>42</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>43</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>46</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>49</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>52</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>55</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>56</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>57</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>58</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>59</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>60</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>61</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>62</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>63</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>64</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>65</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>66</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>67</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.25">
@@ -962,16 +945,16 @@
         <v>1011</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2">
         <v>1990</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -1013,121 +996,121 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>74</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>76</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>77</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>78</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>79</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>80</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>81</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>82</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>83</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>84</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>85</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>86</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>87</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>88</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>89</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>90</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>91</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>92</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>93</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>94</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>95</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>96</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>97</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>98</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>99</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>100</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL1" t="s">
         <v>101</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AM1" t="s">
         <v>102</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.25">
@@ -1144,10 +1127,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1165,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N2">
         <v>10.433070866141732</v>
@@ -1183,28 +1166,28 @@
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" t="s">
-        <v>76</v>
-      </c>
       <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
       </c>
       <c r="I1" t="s">
         <v>0</v>
@@ -1216,190 +1199,190 @@
         <v>2</v>
       </c>
       <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>34</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>35</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>36</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>37</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>40</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>41</v>
       </c>
-      <c r="AS1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV1" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX1" t="s">
         <v>45</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>46</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>47</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>48</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>49</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>50</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>51</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF1" t="s">
         <v>52</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BG1" t="s">
         <v>53</v>
       </c>
-      <c r="BE1" t="s">
-        <v>109</v>
-      </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>54</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>55</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>56</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>57</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>58</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>59</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>60</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>61</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>62</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>63</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>64</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>65</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>66</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>67</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:73" x14ac:dyDescent="0.25">
@@ -1410,10 +1393,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E2">
         <v>101</v>
@@ -1422,13 +1405,13 @@
         <v>1011</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>1990</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q2">
         <v>6</v>
